--- a/data/trans_orig/Q31A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular</t>
+          <t>Edad media en que comenzó a tomar bebidas alcohólicas de forma regular (tasa de respuesta: 98,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,15</t>
+          <t>16,81; 17,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,57</t>
+          <t>17,06; 17,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,28</t>
+          <t>16,75; 17,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 18,23</t>
+          <t>17,61; 18,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 19,51</t>
+          <t>18,27; 19,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 19,93</t>
+          <t>18,14; 19,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,98</t>
+          <t>17,21; 17,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 17,39</t>
+          <t>17,1; 17,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 18,0</t>
+          <t>17,49; 18,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 17,9</t>
+          <t>17,23; 17,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,02</t>
+          <t>16,66; 17,05</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 17,46</t>
+          <t>17,0; 17,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,29</t>
+          <t>16,8; 17,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,13</t>
+          <t>16,66; 17,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 18,47</t>
+          <t>17,75; 18,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 19,55</t>
+          <t>18,14; 19,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 19,13</t>
+          <t>17,97; 19,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 19,2</t>
+          <t>17,92; 19,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,49</t>
+          <t>17,14; 17,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 18,01</t>
+          <t>17,47; 18,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,83</t>
+          <t>17,33; 17,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 17,64</t>
+          <t>17,1; 17,61</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 17,62</t>
+          <t>17,15; 17,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,14; 17,93</t>
+          <t>17,15; 17,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,01</t>
+          <t>16,58; 17,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,63</t>
+          <t>16,98; 17,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 19,08</t>
+          <t>17,99; 19,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,56; 20,33</t>
+          <t>18,57; 20,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 18,69</t>
+          <t>17,51; 18,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 19,31</t>
+          <t>16,39; 19,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,93</t>
+          <t>17,47; 17,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,38</t>
+          <t>17,69; 18,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,47</t>
+          <t>16,97; 17,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 18,02</t>
+          <t>16,55; 18,01</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 17,39</t>
+          <t>17,04; 17,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,9</t>
+          <t>17,18; 17,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,42</t>
+          <t>16,96; 17,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 18,12</t>
+          <t>17,39; 18,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,68</t>
+          <t>17,88; 18,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 19,18</t>
+          <t>18,22; 19,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,81</t>
+          <t>18,52; 19,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 19,35</t>
+          <t>18,38; 19,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 17,78</t>
+          <t>17,41; 17,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,22</t>
+          <t>17,66; 18,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,27</t>
+          <t>17,67; 18,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,89; 18,44</t>
+          <t>17,89; 18,46</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,18</t>
+          <t>17,01; 17,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,52</t>
+          <t>17,21; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,27</t>
+          <t>16,99; 17,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,37</t>
+          <t>17,95; 18,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 19,1</t>
+          <t>18,5; 19,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,31; 18,93</t>
+          <t>18,31; 18,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,63</t>
+          <t>17,07; 18,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 17,53</t>
+          <t>17,35; 17,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 17,97</t>
+          <t>17,69; 17,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,74</t>
+          <t>17,46; 17,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 17,65</t>
+          <t>17,12; 17,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q31A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q31A-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,54</t>
+          <t>16,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>17,69</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17,24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17,72</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>17,51</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17,24</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17,72</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17,51</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,85</t>
+          <t>16,93</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,13</t>
+          <t>16,81; 17,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 17,57</t>
+          <t>17,07; 17,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,75; 17,29</t>
+          <t>16,74; 17,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,73</t>
+          <t>16,38; 16,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 18,2</t>
+          <t>17,62; 18,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 19,53</t>
+          <t>18,24; 19,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 19,93</t>
+          <t>18,14; 19,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,93</t>
+          <t>17,31; 18,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,39</t>
+          <t>17,09; 17,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,49; 18,03</t>
+          <t>17,46; 18,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 17,86</t>
+          <t>17,26; 17,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,05</t>
+          <t>16,75; 17,12</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,88</t>
+          <t>16,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,47</t>
+          <t>18,45</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,35</t>
+          <t>17,41</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 17,46</t>
+          <t>17,03; 17,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,28</t>
+          <t>16,79; 17,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,14</t>
+          <t>16,76; 17,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 18,5</t>
+          <t>17,77; 18,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 19,42</t>
+          <t>18,14; 19,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 19,06</t>
+          <t>17,97; 19,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 19,19</t>
+          <t>17,87; 19,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 17,51</t>
+          <t>17,13; 17,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 18,01</t>
+          <t>17,48; 17,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,86</t>
+          <t>17,3; 17,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,61</t>
+          <t>17,19; 17,67</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,28</t>
+          <t>17,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>19,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,33</t>
+          <t>17,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,62</t>
+          <t>17,13; 17,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,9</t>
+          <t>17,15; 17,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 17,0</t>
+          <t>16,57; 17,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,58</t>
+          <t>17,08; 17,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,11</t>
+          <t>17,98; 19,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,57; 20,32</t>
+          <t>18,54; 20,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 18,75</t>
+          <t>17,52; 18,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,33</t>
+          <t>18,42; 19,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,92</t>
+          <t>17,46; 17,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,4</t>
+          <t>17,65; 18,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 17,47</t>
+          <t>17,0; 17,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 18,01</t>
+          <t>17,65; 18,33</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>17,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,81</t>
+          <t>18,85</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,14</t>
+          <t>18,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,39</t>
+          <t>17,02; 17,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,87</t>
+          <t>17,19; 17,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 17,41</t>
+          <t>16,98; 17,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,12</t>
+          <t>17,37; 18,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 18,65</t>
+          <t>17,88; 18,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 19,21</t>
+          <t>18,26; 19,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,78</t>
+          <t>18,5; 19,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,29</t>
+          <t>18,4; 19,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,78</t>
+          <t>17,42; 17,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,22</t>
+          <t>17,66; 18,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,24</t>
+          <t>17,69; 18,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,89; 18,46</t>
+          <t>17,91; 18,47</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,12</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,47</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,01; 17,2</t>
+          <t>17,0; 17,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,5</t>
+          <t>17,22; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,13</t>
+          <t>16,89; 17,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 17,29</t>
+          <t>17,02; 17,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,35</t>
+          <t>17,96; 18,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,16</t>
+          <t>18,48; 19,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,31; 18,9</t>
+          <t>18,3; 18,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 18,64</t>
+          <t>18,34; 18,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,54</t>
+          <t>17,34; 17,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 17,98</t>
+          <t>17,68; 17,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,72</t>
+          <t>17,45; 17,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 17,67</t>
+          <t>17,52; 17,8</t>
         </is>
       </c>
     </row>
